--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260731.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.71%</t>
+          <t>9.04%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>7.77%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.42%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台指期貨</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>17,833,000</t>
+          <t>1,940</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.89%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6,419,000</t>
+          <t>17,833,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>4.87%</t>
         </is>
       </c>
     </row>
@@ -721,100 +721,100 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,449,000</t>
+          <t>2,564,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.92%</t>
+          <t>4.80%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,443,000</t>
+          <t>6,419,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>4.74%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>25,437,000</t>
+          <t>5,666,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.76%</t>
+          <t>4.56%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,496,000</t>
+          <t>2,443,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.48%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>87,718,000</t>
+          <t>25,437,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>4.43%</t>
         </is>
       </c>
     </row>
@@ -831,51 +831,51 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>4,898,848</t>
+          <t>5,130,848</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,642,000</t>
+          <t>87,718,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>16,327,000</t>
+          <t>5,932,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,374 +887,374 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>9,519,000</t>
+          <t>16,327,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2,297,000</t>
+          <t>9,519,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>454,900</t>
+          <t>2,375,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>7,579,000</t>
+          <t>454,900</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>5,229,000</t>
+          <t>7,579,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,957,000</t>
+          <t>5,229,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,297,000</t>
+          <t>1,957,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>7,543,450</t>
+          <t>2,297,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>7,543,450</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>528,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,874,000</t>
+          <t>348,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>528,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,682,000</t>
+          <t>1,874,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>1,682,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,610,000</t>
+          <t>261,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,470,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,822,000</t>
+          <t>3,250,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1276,46 +1276,46 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>2,224,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,508,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,44 +1349,44 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>526,000</t>
+          <t>1,508,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>1,880,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1415,34 +1415,34 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1723,35 +1723,39 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18,446,431,242</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr"/>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>500,781,127</t>
+          <t>20,141,291,594</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1759,20 +1763,38 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>M_NTD</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>4,182,488,006</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
           <t>RDI_NTD</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>-1,753,850,308</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr"/>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>-4,728,297,749</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
